--- a/data/trans_bre/P5B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Habitat-trans_bre.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,32</t>
+          <t>-3,09; 2,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,59</t>
+          <t>-1,48; 3,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-1,78; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-35,23%</t>
+          <t>-35,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 4,44</t>
+          <t>-3,92; 4,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 3,55</t>
+          <t>-3,39; 3,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,13</t>
+          <t>-2,14; 1,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 167,68</t>
+          <t>-61,79; 177,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,81; 330,55</t>
+          <t>-75,78; 230,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>210,65%</t>
+          <t>213,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,47</t>
+          <t>-1,29; 3,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,69</t>
+          <t>-3,11; 1,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,67</t>
+          <t>-0,4; 5,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 48,08</t>
+          <t>0,5; 51,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,08; —</t>
+          <t>-69,35; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,77</t>
+          <t>-2,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -937,17 +937,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>142,59%</t>
+          <t>141,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-60,39%</t>
+          <t>-60,42%</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 6,62</t>
+          <t>-1,74; 6,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,43</t>
+          <t>-0,79; 5,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,65</t>
+          <t>-1,75; 2,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -0,01</t>
+          <t>-6,32; 0,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 301,04</t>
+          <t>-39,13; 322,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,86; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,73; 23,35</t>
+          <t>-90,08; 18,75</t>
         </is>
       </c>
     </row>
@@ -1037,17 +1037,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>267,31%</t>
+          <t>266,94%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,88</t>
+          <t>-0,86; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,69</t>
+          <t>-0,84; 1,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,83</t>
+          <t>-0,44; 1,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 18,1</t>
+          <t>-0,93; 14,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 132,85</t>
+          <t>-24,23; 123,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 158,5</t>
+          <t>-43,07; 200,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 289,72</t>
+          <t>-27,02; 274,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 1757,94</t>
+          <t>-65,67; 2583,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Habitat-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,99</t>
+          <t>-2,94; 3,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,17 +670,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,52</t>
+          <t>-1,47; 4,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,0</t>
+          <t>-2,19; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 577,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 4,35</t>
+          <t>-3,82; 4,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 3,5</t>
+          <t>-3,28; 3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,13</t>
+          <t>-2,28; 1,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-1,85; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,79; 177,53</t>
+          <t>-64,12; 165,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,78; 230,49</t>
+          <t>-72,52; 243,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,87</t>
+          <t>-1,22; 3,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,43</t>
+          <t>-2,95; 1,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,67</t>
+          <t>-0,27; 5,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 51,32</t>
+          <t>0,48; 52,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-69,35; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 6,1</t>
+          <t>-1,83; 5,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,15</t>
+          <t>-0,69; 5,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,94</t>
+          <t>-1,9; 2,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,06</t>
+          <t>-6,37; -0,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,13; 322,23</t>
+          <t>-44,06; 283,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,3; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,08; 18,75</t>
+          <t>-88,86; 17,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,8</t>
+          <t>-0,91; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,86</t>
+          <t>-0,95; 1,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,83</t>
+          <t>-0,41; 1,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 14,85</t>
+          <t>-0,92; 17,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 123,67</t>
+          <t>-25,29; 118,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 200,01</t>
+          <t>-45,73; 217,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 274,41</t>
+          <t>-29,29; 319,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-65,67; 2583,94</t>
+          <t>-63,75; 3077,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,17</t>
+          <t>-2,79; 3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,17 +670,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,19</t>
+          <t>-1,46; 3,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,0</t>
+          <t>-1,79; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 577,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,07</t>
+          <t>-4,18; 4,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,53</t>
+          <t>-3,27; 3,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,12</t>
+          <t>-2,21; 1,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,0</t>
+          <t>-2,28; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 165,67</t>
+          <t>-61,73; 167,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,52; 243,71</t>
+          <t>-74,5; 300,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,83</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,63</t>
+          <t>-1,29; 3,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,4</t>
+          <t>-2,75; 1,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 5,43</t>
+          <t>-0,46; 5,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 52,52</t>
+          <t>0,45; 10,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,78</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-60,42%</t>
+          <t>-59,75%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 5,92</t>
+          <t>-1,42; 6,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,04</t>
+          <t>-0,69; 5,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,72</t>
+          <t>-1,63; 2,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -0,07</t>
+          <t>-6,25; 0,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,06; 283,25</t>
+          <t>-34,28; 301,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,3; —</t>
+          <t>-53,35; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-94,46; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,86; 17,11</t>
+          <t>-89,09; 16,35</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>266,94%</t>
+          <t>-13,03%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,8</t>
+          <t>-0,96; 2,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,84</t>
+          <t>-0,84; 1,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,97</t>
+          <t>-0,49; 1,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 17,02</t>
+          <t>-1,19; 1,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 118,67</t>
+          <t>-24,52; 132,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 217,33</t>
+          <t>-43,94; 193,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 319,89</t>
+          <t>-36,16; 275,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 3077,27</t>
+          <t>-67,5; 204,05</t>
         </is>
       </c>
     </row>
